--- a/sources/eddy_step3.xlsx
+++ b/sources/eddy_step3.xlsx
@@ -685,6 +685,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
@@ -722,6 +727,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
@@ -757,6 +767,11 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>89b9a62a-0e17-41f7-9bcd-95c83f81b48a</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -9194,6 +9209,11 @@
           <t>mmmhhmmmhmmm</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr">
         <is>
           <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
@@ -9221,6 +9241,11 @@
           <t>mmmhhL</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr">
         <is>
           <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
@@ -9236,6 +9261,11 @@
       <c r="A186" t="inlineStr">
         <is>
           <t>– Leg Whip Series</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>b321b883-5528-4383-9e3a-01d93e60f6ab</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
